--- a/templates/productie/productie_geologie_template.xlsx
+++ b/templates/productie/productie_geologie_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13853" uniqueCount="2030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13850" uniqueCount="2030">
   <si>
     <t>identificatie</t>
   </si>
@@ -6080,25 +6080,25 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-02-10 16:31:11.543728</t>
+    <t>2026-03-31 16:50:51.666315</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.2.3</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>9.4.3</t>
+    <t>10.1.0</t>
   </si>
   <si>
     <t>schema-version</t>
   </si>
   <si>
-    <t>5.9.0</t>
+    <t>5.10.0</t>
   </si>
   <si>
     <t>mode</t>
@@ -49850,7 +49850,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BG6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54.7109375" style="3" customWidth="1"/>
@@ -49910,10 +49910,9 @@
     <col min="57" max="57" width="34.7109375" style="3" customWidth="1"/>
     <col min="58" max="58" width="48.7109375" style="3" customWidth="1"/>
     <col min="59" max="59" width="40.7109375" customWidth="1"/>
-    <col min="60" max="60" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" hidden="1">
+    <row r="1" spans="1:59" hidden="1">
       <c r="A1" s="6" t="s">
         <v>1714</v>
       </c>
@@ -50091,11 +50090,8 @@
       <c r="BG1" s="1" t="s">
         <v>1600</v>
       </c>
-      <c r="BH1" s="1" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="2" spans="1:60" hidden="1">
+    </row>
+    <row r="2" spans="1:59" hidden="1">
       <c r="A2" s="7" t="s">
         <v>1715</v>
       </c>
@@ -50183,11 +50179,8 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
-      <c r="BH2" s="1" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" hidden="1">
+    </row>
+    <row r="3" spans="1:59" hidden="1">
       <c r="A3" s="7" t="s">
         <v>1715</v>
       </c>
@@ -50302,7 +50295,7 @@
       </c>
       <c r="BG3" s="1"/>
     </row>
-    <row r="4" spans="1:60" hidden="1">
+    <row r="4" spans="1:59" hidden="1">
       <c r="E4" s="7" t="s">
         <v>1604</v>
       </c>
@@ -50385,7 +50378,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="5" spans="1:60" hidden="1">
+    <row r="5" spans="1:59" hidden="1">
       <c r="K5" s="7" t="s">
         <v>1732</v>
       </c>
@@ -50438,7 +50431,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="6" spans="1:60">
+    <row r="6" spans="1:59">
       <c r="A6" s="6" t="s">
         <v>1714</v>
       </c>
@@ -50615,9 +50608,6 @@
       </c>
       <c r="BG6" s="1" t="s">
         <v>1600</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>1723</v>
       </c>
     </row>
   </sheetData>

--- a/templates/productie/productie_geologie_template.xlsx
+++ b/templates/productie/productie_geologie_template.xlsx
@@ -6080,13 +6080,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-03-31 16:50:51.666315</t>
+    <t>2026-05-06 16:21:15.712766</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.3.1</t>
   </si>
   <si>
     <t>xdov-version</t>

--- a/templates/productie/productie_geologie_template.xlsx
+++ b/templates/productie/productie_geologie_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13850" uniqueCount="2030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13854" uniqueCount="2032">
   <si>
     <t>identificatie</t>
   </si>
@@ -5735,6 +5735,12 @@
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bam</t>
   </si>
   <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbb</t>
+  </si>
+  <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbo</t>
+  </si>
+  <si>
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/boc</t>
   </si>
   <si>
@@ -6080,19 +6086,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:15.712766</t>
+    <t>2026-05-19 11:28:47.625799</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>
@@ -6415,7 +6421,7 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="Table27" displayName="Table27" ref="BA3:BB12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="Table27" displayName="Table27" ref="BA3:BB14" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Beschrijving"/>
@@ -6971,7 +6977,7 @@
       <c r="AS1" s="1"/>
       <c r="AT1" s="1"/>
       <c r="AU1" s="1" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
@@ -7131,15 +7137,15 @@
       </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="BL2" s="1"/>
       <c r="BM2" s="1" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1" t="s">
@@ -7159,11 +7165,11 @@
       </c>
       <c r="BV2" s="1"/>
       <c r="BW2" s="1" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="BX2" s="1"/>
       <c r="BY2" s="1" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="BZ2" s="1"/>
       <c r="CA2" s="1" t="s">
@@ -7577,13 +7583,13 @@
         <v>59</v>
       </c>
       <c r="BC4" s="2" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="BD4" t="s">
         <v>59</v>
       </c>
       <c r="BE4" s="2" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="BF4" t="s">
         <v>59</v>
@@ -7631,7 +7637,7 @@
         <v>59</v>
       </c>
       <c r="BU4" s="2" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="BV4" t="s">
         <v>59</v>
@@ -7819,13 +7825,13 @@
         <v>59</v>
       </c>
       <c r="BC5" s="2" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="BD5" t="s">
         <v>59</v>
       </c>
       <c r="BE5" s="2" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="BF5" t="s">
         <v>59</v>
@@ -7873,7 +7879,7 @@
         <v>59</v>
       </c>
       <c r="BU5" s="2" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="BV5" t="s">
         <v>59</v>
@@ -8049,13 +8055,13 @@
         <v>59</v>
       </c>
       <c r="BC6" s="2" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="BD6" t="s">
         <v>59</v>
       </c>
       <c r="BE6" s="2" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="BF6" t="s">
         <v>59</v>
@@ -8103,7 +8109,7 @@
         <v>59</v>
       </c>
       <c r="BU6" s="2" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="BV6" t="s">
         <v>59</v>
@@ -8249,7 +8255,7 @@
         <v>59</v>
       </c>
       <c r="BC7" s="2" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="BD7" t="s">
         <v>59</v>
@@ -8431,7 +8437,7 @@
         <v>59</v>
       </c>
       <c r="BC8" s="2" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="BD8" t="s">
         <v>59</v>
@@ -8601,7 +8607,7 @@
         <v>59</v>
       </c>
       <c r="BC9" s="2" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="BD9" t="s">
         <v>59</v>
@@ -8765,7 +8771,7 @@
         <v>59</v>
       </c>
       <c r="BC10" s="2" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="BD10" t="s">
         <v>59</v>
@@ -8929,7 +8935,7 @@
         <v>59</v>
       </c>
       <c r="BC11" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="BD11" t="s">
         <v>59</v>
@@ -9087,7 +9093,7 @@
         <v>59</v>
       </c>
       <c r="BC12" s="2" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="BD12" t="s">
         <v>59</v>
@@ -9238,8 +9244,14 @@
       <c r="AZ13" t="s">
         <v>59</v>
       </c>
+      <c r="BA13" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>59</v>
+      </c>
       <c r="BC13" s="2" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="BD13" t="s">
         <v>59</v>
@@ -9390,8 +9402,14 @@
       <c r="AZ14" t="s">
         <v>59</v>
       </c>
+      <c r="BA14" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>59</v>
+      </c>
       <c r="BC14" s="2" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="BD14" t="s">
         <v>59</v>
@@ -9543,7 +9561,7 @@
         <v>59</v>
       </c>
       <c r="BC15" s="2" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="BD15" t="s">
         <v>59</v>
@@ -9695,7 +9713,7 @@
         <v>59</v>
       </c>
       <c r="BC16" s="2" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="BD16" t="s">
         <v>59</v>
@@ -9847,7 +9865,7 @@
         <v>59</v>
       </c>
       <c r="BC17" s="2" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="BD17" t="s">
         <v>59</v>
@@ -9993,7 +10011,7 @@
         <v>59</v>
       </c>
       <c r="BC18" s="2" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="BD18" t="s">
         <v>59</v>
@@ -10133,7 +10151,7 @@
         <v>59</v>
       </c>
       <c r="BC19" s="2" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="BD19" t="s">
         <v>59</v>
@@ -10273,7 +10291,7 @@
         <v>59</v>
       </c>
       <c r="BC20" s="2" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="BD20" t="s">
         <v>59</v>
@@ -10413,7 +10431,7 @@
         <v>59</v>
       </c>
       <c r="BC21" s="2" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="BD21" t="s">
         <v>59</v>
@@ -10553,7 +10571,7 @@
         <v>59</v>
       </c>
       <c r="BC22" s="2" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="BD22" t="s">
         <v>59</v>
@@ -10693,7 +10711,7 @@
         <v>59</v>
       </c>
       <c r="BC23" s="2" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="BD23" t="s">
         <v>59</v>
@@ -10827,7 +10845,7 @@
         <v>59</v>
       </c>
       <c r="BC24" s="2" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="BD24" t="s">
         <v>59</v>
@@ -10961,7 +10979,7 @@
         <v>59</v>
       </c>
       <c r="BC25" s="2" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="BD25" t="s">
         <v>59</v>
@@ -11095,7 +11113,7 @@
         <v>59</v>
       </c>
       <c r="BC26" s="2" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="BD26" t="s">
         <v>59</v>
@@ -11229,7 +11247,7 @@
         <v>59</v>
       </c>
       <c r="BC27" s="2" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="BD27" t="s">
         <v>59</v>
@@ -11363,7 +11381,7 @@
         <v>59</v>
       </c>
       <c r="BC28" s="2" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="BD28" t="s">
         <v>59</v>
@@ -11497,7 +11515,7 @@
         <v>59</v>
       </c>
       <c r="BC29" s="2" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="BD29" t="s">
         <v>59</v>
@@ -11625,7 +11643,7 @@
         <v>59</v>
       </c>
       <c r="BC30" s="2" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="BD30" t="s">
         <v>59</v>
@@ -11741,7 +11759,7 @@
         <v>59</v>
       </c>
       <c r="BC31" s="2" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="BD31" t="s">
         <v>59</v>
@@ -11857,7 +11875,7 @@
         <v>59</v>
       </c>
       <c r="BC32" s="2" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="BD32" t="s">
         <v>59</v>
@@ -11973,7 +11991,7 @@
         <v>59</v>
       </c>
       <c r="BC33" s="2" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="BD33" t="s">
         <v>59</v>
@@ -12089,7 +12107,7 @@
         <v>59</v>
       </c>
       <c r="BC34" s="2" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="BD34" t="s">
         <v>59</v>
@@ -12205,7 +12223,7 @@
         <v>59</v>
       </c>
       <c r="BC35" s="2" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="BD35" t="s">
         <v>59</v>
@@ -12321,7 +12339,7 @@
         <v>59</v>
       </c>
       <c r="BC36" s="2" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="BD36" t="s">
         <v>59</v>
@@ -12437,7 +12455,7 @@
         <v>59</v>
       </c>
       <c r="BC37" s="2" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="BD37" t="s">
         <v>59</v>
@@ -12553,7 +12571,7 @@
         <v>59</v>
       </c>
       <c r="BC38" s="2" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="BD38" t="s">
         <v>59</v>
@@ -12669,7 +12687,7 @@
         <v>59</v>
       </c>
       <c r="BC39" s="2" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="BD39" t="s">
         <v>59</v>
@@ -12785,7 +12803,7 @@
         <v>59</v>
       </c>
       <c r="BC40" s="2" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="BD40" t="s">
         <v>59</v>
@@ -48403,113 +48421,113 @@
     <hyperlink ref="BA12" r:id="rId32"/>
     <hyperlink ref="BC12" r:id="rId33"/>
     <hyperlink ref="AY13" r:id="rId34"/>
-    <hyperlink ref="BC13" r:id="rId35"/>
-    <hyperlink ref="AY14" r:id="rId36"/>
-    <hyperlink ref="BC14" r:id="rId37"/>
-    <hyperlink ref="AY15" r:id="rId38"/>
-    <hyperlink ref="BC15" r:id="rId39"/>
-    <hyperlink ref="AY16" r:id="rId40"/>
-    <hyperlink ref="BC16" r:id="rId41"/>
-    <hyperlink ref="AY17" r:id="rId42"/>
-    <hyperlink ref="BC17" r:id="rId43"/>
-    <hyperlink ref="AY18" r:id="rId44"/>
-    <hyperlink ref="BC18" r:id="rId45"/>
-    <hyperlink ref="AY19" r:id="rId46"/>
-    <hyperlink ref="BC19" r:id="rId47"/>
-    <hyperlink ref="AY20" r:id="rId48"/>
-    <hyperlink ref="BC20" r:id="rId49"/>
-    <hyperlink ref="AY21" r:id="rId50"/>
-    <hyperlink ref="BC21" r:id="rId51"/>
-    <hyperlink ref="AY22" r:id="rId52"/>
-    <hyperlink ref="BC22" r:id="rId53"/>
-    <hyperlink ref="AY23" r:id="rId54"/>
-    <hyperlink ref="BC23" r:id="rId55"/>
-    <hyperlink ref="AY24" r:id="rId56"/>
-    <hyperlink ref="BC24" r:id="rId57"/>
-    <hyperlink ref="AY25" r:id="rId58"/>
-    <hyperlink ref="BC25" r:id="rId59"/>
-    <hyperlink ref="AY26" r:id="rId60"/>
-    <hyperlink ref="BC26" r:id="rId61"/>
-    <hyperlink ref="AY27" r:id="rId62"/>
-    <hyperlink ref="BC27" r:id="rId63"/>
-    <hyperlink ref="AY28" r:id="rId64"/>
-    <hyperlink ref="BC28" r:id="rId65"/>
-    <hyperlink ref="AY29" r:id="rId66"/>
-    <hyperlink ref="BC29" r:id="rId67"/>
-    <hyperlink ref="AY30" r:id="rId68"/>
-    <hyperlink ref="BC30" r:id="rId69"/>
-    <hyperlink ref="AY31" r:id="rId70"/>
-    <hyperlink ref="BC31" r:id="rId71"/>
-    <hyperlink ref="AY32" r:id="rId72"/>
-    <hyperlink ref="BC32" r:id="rId73"/>
-    <hyperlink ref="AY33" r:id="rId74"/>
-    <hyperlink ref="BC33" r:id="rId75"/>
-    <hyperlink ref="AY34" r:id="rId76"/>
-    <hyperlink ref="BC34" r:id="rId77"/>
-    <hyperlink ref="AY35" r:id="rId78"/>
-    <hyperlink ref="BC35" r:id="rId79"/>
-    <hyperlink ref="AY36" r:id="rId80"/>
-    <hyperlink ref="BC36" r:id="rId81"/>
-    <hyperlink ref="AY37" r:id="rId82"/>
-    <hyperlink ref="BC37" r:id="rId83"/>
-    <hyperlink ref="AY38" r:id="rId84"/>
-    <hyperlink ref="BC38" r:id="rId85"/>
-    <hyperlink ref="AY39" r:id="rId86"/>
-    <hyperlink ref="BC39" r:id="rId87"/>
-    <hyperlink ref="AY40" r:id="rId88"/>
-    <hyperlink ref="BC40" r:id="rId89"/>
-    <hyperlink ref="AY41" r:id="rId90"/>
-    <hyperlink ref="AY42" r:id="rId91"/>
-    <hyperlink ref="AY43" r:id="rId92"/>
-    <hyperlink ref="AY44" r:id="rId93"/>
-    <hyperlink ref="AY45" r:id="rId94"/>
-    <hyperlink ref="AY46" r:id="rId95"/>
-    <hyperlink ref="AY47" r:id="rId96"/>
-    <hyperlink ref="AY48" r:id="rId97"/>
-    <hyperlink ref="AY49" r:id="rId98"/>
-    <hyperlink ref="AY50" r:id="rId99"/>
-    <hyperlink ref="AY51" r:id="rId100"/>
-    <hyperlink ref="AY52" r:id="rId101"/>
-    <hyperlink ref="AY53" r:id="rId102"/>
-    <hyperlink ref="AY54" r:id="rId103"/>
-    <hyperlink ref="AY55" r:id="rId104"/>
-    <hyperlink ref="AY56" r:id="rId105"/>
-    <hyperlink ref="AY57" r:id="rId106"/>
-    <hyperlink ref="AY58" r:id="rId107"/>
-    <hyperlink ref="AY59" r:id="rId108"/>
-    <hyperlink ref="AY60" r:id="rId109"/>
-    <hyperlink ref="AY61" r:id="rId110"/>
-    <hyperlink ref="AY62" r:id="rId111"/>
-    <hyperlink ref="AY63" r:id="rId112"/>
-    <hyperlink ref="AY64" r:id="rId113"/>
-    <hyperlink ref="AY65" r:id="rId114"/>
-    <hyperlink ref="AY66" r:id="rId115"/>
-    <hyperlink ref="AY67" r:id="rId116"/>
-    <hyperlink ref="AY68" r:id="rId117"/>
-    <hyperlink ref="AY69" r:id="rId118"/>
-    <hyperlink ref="AY70" r:id="rId119"/>
-    <hyperlink ref="AY71" r:id="rId120"/>
-    <hyperlink ref="AY72" r:id="rId121"/>
-    <hyperlink ref="AY73" r:id="rId122"/>
-    <hyperlink ref="AY74" r:id="rId123"/>
-    <hyperlink ref="AY75" r:id="rId124"/>
-    <hyperlink ref="AY76" r:id="rId125"/>
-    <hyperlink ref="AY77" r:id="rId126"/>
-    <hyperlink ref="AY78" r:id="rId127"/>
-    <hyperlink ref="AY79" r:id="rId128"/>
-    <hyperlink ref="AY80" r:id="rId129"/>
-    <hyperlink ref="AY81" r:id="rId130"/>
-    <hyperlink ref="AY82" r:id="rId131"/>
-    <hyperlink ref="AY83" r:id="rId132"/>
-    <hyperlink ref="AY84" r:id="rId133"/>
-    <hyperlink ref="AY85" r:id="rId134"/>
-    <hyperlink ref="AY86" r:id="rId135"/>
-    <hyperlink ref="AY87" r:id="rId136"/>
+    <hyperlink ref="BA13" r:id="rId35"/>
+    <hyperlink ref="BC13" r:id="rId36"/>
+    <hyperlink ref="AY14" r:id="rId37"/>
+    <hyperlink ref="BA14" r:id="rId38"/>
+    <hyperlink ref="BC14" r:id="rId39"/>
+    <hyperlink ref="AY15" r:id="rId40"/>
+    <hyperlink ref="BC15" r:id="rId41"/>
+    <hyperlink ref="AY16" r:id="rId42"/>
+    <hyperlink ref="BC16" r:id="rId43"/>
+    <hyperlink ref="AY17" r:id="rId44"/>
+    <hyperlink ref="BC17" r:id="rId45"/>
+    <hyperlink ref="AY18" r:id="rId46"/>
+    <hyperlink ref="BC18" r:id="rId47"/>
+    <hyperlink ref="AY19" r:id="rId48"/>
+    <hyperlink ref="BC19" r:id="rId49"/>
+    <hyperlink ref="AY20" r:id="rId50"/>
+    <hyperlink ref="BC20" r:id="rId51"/>
+    <hyperlink ref="AY21" r:id="rId52"/>
+    <hyperlink ref="BC21" r:id="rId53"/>
+    <hyperlink ref="AY22" r:id="rId54"/>
+    <hyperlink ref="BC22" r:id="rId55"/>
+    <hyperlink ref="AY23" r:id="rId56"/>
+    <hyperlink ref="BC23" r:id="rId57"/>
+    <hyperlink ref="AY24" r:id="rId58"/>
+    <hyperlink ref="BC24" r:id="rId59"/>
+    <hyperlink ref="AY25" r:id="rId60"/>
+    <hyperlink ref="BC25" r:id="rId61"/>
+    <hyperlink ref="AY26" r:id="rId62"/>
+    <hyperlink ref="BC26" r:id="rId63"/>
+    <hyperlink ref="AY27" r:id="rId64"/>
+    <hyperlink ref="BC27" r:id="rId65"/>
+    <hyperlink ref="AY28" r:id="rId66"/>
+    <hyperlink ref="BC28" r:id="rId67"/>
+    <hyperlink ref="AY29" r:id="rId68"/>
+    <hyperlink ref="BC29" r:id="rId69"/>
+    <hyperlink ref="AY30" r:id="rId70"/>
+    <hyperlink ref="BC30" r:id="rId71"/>
+    <hyperlink ref="AY31" r:id="rId72"/>
+    <hyperlink ref="BC31" r:id="rId73"/>
+    <hyperlink ref="AY32" r:id="rId74"/>
+    <hyperlink ref="BC32" r:id="rId75"/>
+    <hyperlink ref="AY33" r:id="rId76"/>
+    <hyperlink ref="BC33" r:id="rId77"/>
+    <hyperlink ref="AY34" r:id="rId78"/>
+    <hyperlink ref="BC34" r:id="rId79"/>
+    <hyperlink ref="AY35" r:id="rId80"/>
+    <hyperlink ref="BC35" r:id="rId81"/>
+    <hyperlink ref="AY36" r:id="rId82"/>
+    <hyperlink ref="BC36" r:id="rId83"/>
+    <hyperlink ref="AY37" r:id="rId84"/>
+    <hyperlink ref="BC37" r:id="rId85"/>
+    <hyperlink ref="AY38" r:id="rId86"/>
+    <hyperlink ref="BC38" r:id="rId87"/>
+    <hyperlink ref="AY39" r:id="rId88"/>
+    <hyperlink ref="BC39" r:id="rId89"/>
+    <hyperlink ref="AY40" r:id="rId90"/>
+    <hyperlink ref="BC40" r:id="rId91"/>
+    <hyperlink ref="AY41" r:id="rId92"/>
+    <hyperlink ref="AY42" r:id="rId93"/>
+    <hyperlink ref="AY43" r:id="rId94"/>
+    <hyperlink ref="AY44" r:id="rId95"/>
+    <hyperlink ref="AY45" r:id="rId96"/>
+    <hyperlink ref="AY46" r:id="rId97"/>
+    <hyperlink ref="AY47" r:id="rId98"/>
+    <hyperlink ref="AY48" r:id="rId99"/>
+    <hyperlink ref="AY49" r:id="rId100"/>
+    <hyperlink ref="AY50" r:id="rId101"/>
+    <hyperlink ref="AY51" r:id="rId102"/>
+    <hyperlink ref="AY52" r:id="rId103"/>
+    <hyperlink ref="AY53" r:id="rId104"/>
+    <hyperlink ref="AY54" r:id="rId105"/>
+    <hyperlink ref="AY55" r:id="rId106"/>
+    <hyperlink ref="AY56" r:id="rId107"/>
+    <hyperlink ref="AY57" r:id="rId108"/>
+    <hyperlink ref="AY58" r:id="rId109"/>
+    <hyperlink ref="AY59" r:id="rId110"/>
+    <hyperlink ref="AY60" r:id="rId111"/>
+    <hyperlink ref="AY61" r:id="rId112"/>
+    <hyperlink ref="AY62" r:id="rId113"/>
+    <hyperlink ref="AY63" r:id="rId114"/>
+    <hyperlink ref="AY64" r:id="rId115"/>
+    <hyperlink ref="AY65" r:id="rId116"/>
+    <hyperlink ref="AY66" r:id="rId117"/>
+    <hyperlink ref="AY67" r:id="rId118"/>
+    <hyperlink ref="AY68" r:id="rId119"/>
+    <hyperlink ref="AY69" r:id="rId120"/>
+    <hyperlink ref="AY70" r:id="rId121"/>
+    <hyperlink ref="AY71" r:id="rId122"/>
+    <hyperlink ref="AY72" r:id="rId123"/>
+    <hyperlink ref="AY73" r:id="rId124"/>
+    <hyperlink ref="AY74" r:id="rId125"/>
+    <hyperlink ref="AY75" r:id="rId126"/>
+    <hyperlink ref="AY76" r:id="rId127"/>
+    <hyperlink ref="AY77" r:id="rId128"/>
+    <hyperlink ref="AY78" r:id="rId129"/>
+    <hyperlink ref="AY79" r:id="rId130"/>
+    <hyperlink ref="AY80" r:id="rId131"/>
+    <hyperlink ref="AY81" r:id="rId132"/>
+    <hyperlink ref="AY82" r:id="rId133"/>
+    <hyperlink ref="AY83" r:id="rId134"/>
+    <hyperlink ref="AY84" r:id="rId135"/>
+    <hyperlink ref="AY85" r:id="rId136"/>
+    <hyperlink ref="AY86" r:id="rId137"/>
+    <hyperlink ref="AY87" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="40">
-    <tablePart r:id="rId137"/>
-    <tablePart r:id="rId138"/>
     <tablePart r:id="rId139"/>
     <tablePart r:id="rId140"/>
     <tablePart r:id="rId141"/>
@@ -48548,6 +48566,8 @@
     <tablePart r:id="rId174"/>
     <tablePart r:id="rId175"/>
     <tablePart r:id="rId176"/>
+    <tablePart r:id="rId177"/>
+    <tablePart r:id="rId178"/>
   </tableParts>
 </worksheet>
 </file>
@@ -50648,7 +50668,7 @@
       <formula1>'Codelijsten'!$AY$4:$AY$87</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:I1000001">
-      <formula1>'Codelijsten'!$BA$4:$BA$12</formula1>
+      <formula1>'Codelijsten'!$BA$4:$BA$14</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7:T1000001">
       <formula1>-146096</formula1>
@@ -50770,58 +50790,58 @@
   <sheetData>
     <row r="1" spans="1:74" hidden="1">
       <c r="A1" s="6" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>1603</v>
@@ -50830,16 +50850,16 @@
         <v>1605</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>1</v>
@@ -50848,7 +50868,7 @@
         <v>2</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>234</v>
@@ -50863,82 +50883,82 @@
         <v>1327</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>43</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>1782</v>
@@ -51020,7 +51040,7 @@
       </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -51032,7 +51052,7 @@
         <v>2</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="AB2" s="1" t="s">
         <v>234</v>
@@ -51047,7 +51067,7 @@
         <v>1327</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>43</v>
@@ -51080,7 +51100,7 @@
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
@@ -51119,7 +51139,7 @@
         <v>228</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -51133,7 +51153,7 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -51161,7 +51181,7 @@
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
@@ -51193,10 +51213,10 @@
         <v>234</v>
       </c>
       <c r="BC3" s="7" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="BD3" s="7" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="BE3" s="1" t="s">
         <v>57</v>
@@ -51240,13 +51260,13 @@
     </row>
     <row r="4" spans="1:74" hidden="1">
       <c r="D4" s="7" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -51256,13 +51276,13 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="1" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -51354,7 +51374,7 @@
         <v>238</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="R5" s="1" t="s">
         <v>240</v>
@@ -51383,16 +51403,16 @@
     </row>
     <row r="6" spans="1:74" hidden="1">
       <c r="F6" s="7" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>246</v>
@@ -51409,58 +51429,58 @@
     </row>
     <row r="7" spans="1:74">
       <c r="A7" s="6" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>1603</v>
@@ -51469,16 +51489,16 @@
         <v>1605</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="Y7" s="1" t="s">
         <v>1</v>
@@ -51487,7 +51507,7 @@
         <v>2</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="AB7" s="1" t="s">
         <v>234</v>
@@ -51502,82 +51522,82 @@
         <v>1327</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="AG7" s="1" t="s">
         <v>43</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="BA7" s="1" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="BB7" s="1" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="BE7" s="1" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="BF7" s="1" t="s">
         <v>1782</v>
@@ -51729,50 +51749,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B1" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B2" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B5" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="B6" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
     </row>
   </sheetData>

--- a/templates/productie/productie_geologie_template.xlsx
+++ b/templates/productie/productie_geologie_template.xlsx
@@ -6086,13 +6086,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:28:47.625799</t>
+    <t>2026-05-19 14:52:40.270960</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
